--- a/Tailieu/Nganhangfilegoc/sao_ke_10.xlsx
+++ b/Tailieu/Nganhangfilegoc/sao_ke_10.xlsx
@@ -31,64 +31,433 @@
     <x:t>Số dư</x:t>
   </x:si>
   <x:si>
-    <x:t>03/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY DIEN MAY CHIEM BON THANH TOAN CHUYEN KHOAN NAM VIET</x:t>
+    <x:t>01/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUU VAN HAI chuyen tien.CT tu 1055943527 LUU VAN HAI toi 6000201008933 Cty TNHH Thuy San Cha Va Long Son tai AGRIBANK</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>CTY TNHH BACH NIEN THIEN DUC VUNG TAU TT TIEN MUA MAY CHAM CONG CUA CTY CHIEM BON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nap vao tai khoan cty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY DIEN MAY CHIEM BON THANH TOAN CHUYEN KHOAN DAI TAI LOC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thanh toan hd 40 cho chiem bon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>My Nam TT phan mem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY TNHH BACH NIEN THIEN DUC VUNG TAU TT TIEN NANG CAP SUA CHUA MAY TINH CHO CTY CHIEM BON THEO HD SO 46 NGAY 6.8.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NGUYEN QUOC HOANG Rut tien tai ACB ATM PGD LE H PHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY TNHH MY THUAT SX DV THUONG MAI PHUONG LONG-THEO HD SO 45 KY NGAY 5/8/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THANH TOAN LUONG THANG 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nap vao tai khoan cong ty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY CHIEM BON THANH TOAN HD 3442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lai nhap von</x:t>
+    <x:t>HA VAN ANH chuyen tien.CT tu 0121001247300 HA VAN ANH toi 6000201008933 Cty TNHH Thuy San Cha Va Long Son tai AGRIBANK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUONG DAC BINH CHUYEN KHOAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRAN VAN BAN chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUI THI TUYEN chuyen tien.CT tu 9905376768 BUI THI TUYEN toi 6000201008933 Cty TNHH Thuy San Cha Va Long Son tai AGRIBANK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Le Van Bien chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau THANH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca HUONG BIEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NGUYEN DUC DUNG chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NGUYEN THI BINH chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca HOANG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca BINH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien cua HOANG TIEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien tom DUNG SY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ngheu HONG NGOC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien so HOANG PHAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca tom TRUONG THANH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca NAM DIEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien nuoc da thang 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHAM THI HUONG chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VTU-02-064573, Vien Thong, 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VTU-01-233071, Vien Thong, 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VTU-02-064879, Vien Thong, 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VTU-01-233070, Vien Thong, 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VTU-01-231754, Vien Thong, 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PB15010137189, Dien, 09/26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VTU-02-064576, Vien Thong, 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6000LDS202600482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NGUYEN THI MAN chuyen tien.CT tu 0081001308557 NGUYEN THI MAN toi 6000201008933 Cty TNHH Thuy San Cha Va Long Son tai AGRIBANK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phi DV SMS Banking T08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bang Lang Quan chuyen khoan nhanh qua Zalo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ton lanh mau</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca MINH CUONG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TT TIEN HAI SAN HD 1281+1268+1261+1255+1239+1219+1220+1227+1200+1180+1191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TT TIEN HAI SAN HD 1282+1242+1253+1262+1271+1181+1190+1189+1201+1216+1228 NGAY 5-9-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TT TIEN HAI SAN HD 1283+1272+1263+1254+1243+1182+1188+1202+1217+1229 NGAY 5-9-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phuoc Nguyen TT tien hang HD 1195 den 1231 Cty Cha Va LS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LE PHU DO chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRAN VAN MUOI-RUT SEC AS7480063</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son tien thue mat bang Q 3 va 4 nam 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hang THANH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca Binh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca HAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau HOI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien tom DUNG SI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh tien so HOANG PHAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thang toan tien cua HOANG TIEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C/C Transfer TO: #6000205272265 : CHI LUONG THANG 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C/C Transfer TO: #6000205717077 : CHI LUONG THANG 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C/C Transfer TO: #6000205877885 : CHI LUONG THANG 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C/C Transfer TO: #6000205877862 : CHI LUONG THANG 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C/C Transfer TO: #6000205870959 : CHI LUONG THANG 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C/C Transfer TO: #6000205639783 : CHI LUONG THANG 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C/C Transfer TO: #6000205663815 : CHI LUONG THANG 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C/C Transfer TO: #6000205717048 : CHI LUONG THANG 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C/C Transfer TO: #6000205717054 : CHI LUONG THANG 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C/C Transfer TO: #6000205660360 : CHI LUONG THANG 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C/C Transfer TO: #6000205877891 : CHI LUONG THANG 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C/C Transfer TO: #6000205487444 : CHI LUONG THANG 08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien mua nhotv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau DUNG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau TUAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau Co LANH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phuoc nguyen TT tien hang HD tu 1247 den 1309 Cty Cha Va LS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NGUYEN HUU TIEN CHUYEN KHOAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ca chim</x:t>
+  </x:si>
+  <x:si>
+    <x:t>so long</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau LANH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan toen ca MINH CUONG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TT TIEN HAI SAN HD 1344+1190+1292+1298+1306+1315+1326+1332 ngay 12-09-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TT TIEN HAI SAN HD 1353+1343+1290+1297+1308+1314+1325+1331 NGAY 13-09-2023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TT TIEN HAI SAN HD 1345+1291+1299+1307+1316+1327+1333 ngay 12-09-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5469532, Nuoc, 9/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca TRUONG THANH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thang toan tien ca HAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca THE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chi dung Zalopay chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien lap camera xe 72 C 02885</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6000LDS202601410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NGUYEN MINH NHAT chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NGUYEN VAN XUAN chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thu phi quan ly tai khoan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAI DUY HOP chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LE VAN TINH CHUYEN KHOAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LE HUY HOANG chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thang toan tien ca MINH CUONG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thwnh toan tilafm n cua HOANG TIEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TT TIEN HAI SAN HD 1419+1354+1359+1369+1378+1389+1402+1408 NGAY 20-09-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TT TIEN HAI SAN HD 1351+1360+1370+1379+1390+1400+1411 NGAY 13-09-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TT TIEN HAI SAN HD 1412+1350+1361+1371+1380+1391+1401 NGAY 19-09-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca HOANGVAF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau THANH ben da</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phuoc Nguyen TT tien hang HD 1319 den 1373 Cty Cha Va LS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LE MANH THANG chuyen tien.CT tu 0081000209112 LE MANH THANG toi 6000201008933 Cty TNHH Thuy San Cha Va Long Son tai AGRIBANK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luong Phu chuyen khoan nhanh qua Zalo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau Quan Quyen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son tam ung mua xang dau</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>le thi nhung chuyen khoan nhanh qua Zalo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LE CONG VUONG chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUYNH PHUC TOAN chuyen tien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau QUYEN QUAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TT TIEN HAI SAN HD 1472+1473+1422+1429+1438+1444+1454+1465 NGAY 26-09-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TT TIEN HAI SAN HD 1474+1420+1430+1436+1446+1455+1461 NGAY 26-09-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TT TIEN HAI SAN HD 1475+1421+1431+1437+1445+1456+1463 NGAY 26-09-2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien cua HOANG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca HOANG Ben Da</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau MINH DUNG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau DUC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau NAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son dich vu khai bao thue Q3 nam 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son nop +BHXH+103+00+Q60027I+07709+dong BHXH thang 9 nam 2026+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son nop +BHXH+103+00+TA2045A+07709+dong BHXH thang 9 nam 2026+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien da cay HONG PHAT 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca THIEN HUONG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien hau THANH Ben da</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cty TNHH Thuy San Cha Va Long Son thanh toan tien ca YEN SUONG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lãi tiền gửi</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -462,13 +831,13 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E15"/>
+  <x:dimension ref="A1:E139"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="123.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="4" width="9.424911" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.424911" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="126.853482" style="0" customWidth="1"/>
+    <x:col min="3" max="4" width="11.424911" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5" s="1" customFormat="1">
@@ -495,14 +864,14 @@
       <x:c r="B2" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C2" s="2">
-        <x:v>1500000</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>7</x:v>
+      <x:c r="C2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D2" s="2">
+        <x:v>185000</x:v>
       </x:c>
       <x:c r="E2" s="2">
-        <x:v>455235</x:v>
+        <x:v>932454224</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -516,10 +885,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="2">
-        <x:v>2500000</x:v>
+        <x:v>793000</x:v>
       </x:c>
       <x:c r="E3" s="2">
-        <x:v>2955235</x:v>
+        <x:v>933247224</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -533,10 +902,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D4" s="2">
-        <x:v>2000000</x:v>
+        <x:v>355000</x:v>
       </x:c>
       <x:c r="E4" s="2">
-        <x:v>4955235</x:v>
+        <x:v>933602224</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
@@ -546,184 +915,2292 @@
       <x:c r="B5" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C5" s="2">
-        <x:v>3900000</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>7</x:v>
+      <x:c r="C5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="2">
+        <x:v>630000</x:v>
       </x:c>
       <x:c r="E5" s="2">
-        <x:v>1055235</x:v>
+        <x:v>934232224</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D6" s="2">
-        <x:v>2500000</x:v>
+        <x:v>240000</x:v>
       </x:c>
       <x:c r="E6" s="2">
-        <x:v>3555235</x:v>
+        <x:v>934472224</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="2">
-        <x:v>5200000</x:v>
+        <x:v>525000</x:v>
       </x:c>
       <x:c r="E7" s="2">
-        <x:v>8755235</x:v>
+        <x:v>934997224</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="2">
-        <x:v>5690000</x:v>
+      <x:c r="C8" s="2">
+        <x:v>28268000</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="2">
-        <x:v>14445235</x:v>
+        <x:v>906729224</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="2">
-        <x:v>6500000</x:v>
+        <x:v>73092058</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E9" s="2">
-        <x:v>7945235</x:v>
+        <x:v>833637166</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D10" s="2">
-        <x:v>2260000</x:v>
+        <x:v>816000</x:v>
       </x:c>
       <x:c r="E10" s="2">
-        <x:v>10205235</x:v>
+        <x:v>834453166</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C11" s="2">
-        <x:v>2250000</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D11" s="2">
+        <x:v>1096000</x:v>
       </x:c>
       <x:c r="E11" s="2">
-        <x:v>7955235</x:v>
+        <x:v>835549166</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="C12" s="2">
-        <x:v>7500000</x:v>
+        <x:v>78772995</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E12" s="2">
-        <x:v>455235</x:v>
+        <x:v>756776171</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D13" s="2">
-        <x:v>1512000</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C13" s="2">
+        <x:v>12870000</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E13" s="2">
-        <x:v>1967235</x:v>
+        <x:v>743906171</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="C14" s="2">
-        <x:v>1296000</x:v>
+        <x:v>21320000</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E14" s="2">
-        <x:v>671235</x:v>
+        <x:v>722586171</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C15" s="2">
+        <x:v>128225654</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E15" s="2">
+        <x:v>594360517</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:5">
+      <x:c r="A16" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C16" s="2">
+        <x:v>5786600</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E16" s="2">
+        <x:v>588573917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:5">
+      <x:c r="A17" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B15" s="0" t="s">
+      <x:c r="C17" s="2">
+        <x:v>5946600</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E17" s="2">
+        <x:v>582627317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:5">
+      <x:c r="A18" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D15" s="2">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E15" s="2">
-        <x:v>671253</x:v>
+      <x:c r="C18" s="2">
+        <x:v>22090000</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E18" s="2">
+        <x:v>560537317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:5">
+      <x:c r="A19" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C19" s="2">
+        <x:v>28005600</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E19" s="2">
+        <x:v>532531717</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:5">
+      <x:c r="A20" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C20" s="2">
+        <x:v>3306600</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E20" s="2">
+        <x:v>529225117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:5">
+      <x:c r="A21" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D21" s="2">
+        <x:v>6897000</x:v>
+      </x:c>
+      <x:c r="E21" s="2">
+        <x:v>536122117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:5">
+      <x:c r="A22" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C22" s="2">
+        <x:v>405968</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E22" s="2">
+        <x:v>535716149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:5">
+      <x:c r="A23" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C23" s="2">
+        <x:v>112765</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E23" s="2">
+        <x:v>535603384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:5">
+      <x:c r="A24" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C24" s="2">
+        <x:v>664000</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E24" s="2">
+        <x:v>534939384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:5">
+      <x:c r="A25" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C25" s="2">
+        <x:v>287005</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E25" s="2">
+        <x:v>534652379</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:5">
+      <x:c r="A26" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C26" s="2">
+        <x:v>150000</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E26" s="2">
+        <x:v>534502379</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:5">
+      <x:c r="A27" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C27" s="2">
+        <x:v>18623507</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E27" s="2">
+        <x:v>515878872</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:5">
+      <x:c r="A28" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C28" s="2">
+        <x:v>364098</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E28" s="2">
+        <x:v>515514774</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:5">
+      <x:c r="A29" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C29" s="2">
+        <x:v>408334246</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E29" s="2">
+        <x:v>107180528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:5">
+      <x:c r="A30" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D30" s="2">
+        <x:v>1716000</x:v>
+      </x:c>
+      <x:c r="E30" s="2">
+        <x:v>108896528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:5">
+      <x:c r="A31" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C31" s="2">
+        <x:v>55000</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E31" s="2">
+        <x:v>108841528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:5">
+      <x:c r="A32" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D32" s="2">
+        <x:v>405000</x:v>
+      </x:c>
+      <x:c r="E32" s="2">
+        <x:v>109246528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:5">
+      <x:c r="A33" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C33" s="2">
+        <x:v>21275000</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E33" s="2">
+        <x:v>87971528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:5">
+      <x:c r="A34" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C34" s="2">
+        <x:v>4983000</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E34" s="2">
+        <x:v>82988528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:5">
+      <x:c r="A35" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C35" s="2">
+        <x:v>62097000</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E35" s="2">
+        <x:v>20891528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:5">
+      <x:c r="A36" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D36" s="2">
+        <x:v>659564500</x:v>
+      </x:c>
+      <x:c r="E36" s="2">
+        <x:v>680456028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:5">
+      <x:c r="A37" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D37" s="2">
+        <x:v>380900750</x:v>
+      </x:c>
+      <x:c r="E37" s="2">
+        <x:v>1061356778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:5">
+      <x:c r="A38" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D38" s="2">
+        <x:v>216848750</x:v>
+      </x:c>
+      <x:c r="E38" s="2">
+        <x:v>1278205528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:5">
+      <x:c r="A39" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D39" s="2">
+        <x:v>13744250</x:v>
+      </x:c>
+      <x:c r="E39" s="2">
+        <x:v>1291949778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:5">
+      <x:c r="A40" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D40" s="2">
+        <x:v>1224000</x:v>
+      </x:c>
+      <x:c r="E40" s="2">
+        <x:v>1293173778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:5">
+      <x:c r="A41" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C41" s="2">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E41" s="2">
+        <x:v>993173778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:5">
+      <x:c r="A42" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C42" s="2">
+        <x:v>150024750</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E42" s="2">
+        <x:v>843149028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:5">
+      <x:c r="A43" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C43" s="2">
+        <x:v>11810000</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E43" s="2">
+        <x:v>831339028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:5">
+      <x:c r="A44" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C44" s="2">
+        <x:v>672000</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E44" s="2">
+        <x:v>830667028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:5">
+      <x:c r="A45" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C45" s="2">
+        <x:v>15070000</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E45" s="2">
+        <x:v>815597028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:5">
+      <x:c r="A46" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C46" s="2">
+        <x:v>41206798</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E46" s="2">
+        <x:v>774390230</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:5">
+      <x:c r="A47" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C47" s="2">
+        <x:v>13036600</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E47" s="2">
+        <x:v>761353630</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:5">
+      <x:c r="A48" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C48" s="2">
+        <x:v>21300600</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E48" s="2">
+        <x:v>740053030</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:5">
+      <x:c r="A49" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C49" s="2">
+        <x:v>44240299</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E49" s="2">
+        <x:v>695812731</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:5">
+      <x:c r="A50" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C50" s="2">
+        <x:v>3606600</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E50" s="2">
+        <x:v>692206131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:5">
+      <x:c r="A51" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C51" s="2">
+        <x:v>22576600</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E51" s="2">
+        <x:v>669629531</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:5">
+      <x:c r="A52" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C52" s="2">
+        <x:v>11155000</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E52" s="2">
+        <x:v>658474531</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:5">
+      <x:c r="A53" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C53" s="2">
+        <x:v>19637308</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E53" s="2">
+        <x:v>638837223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:5">
+      <x:c r="A54" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C54" s="2">
+        <x:v>15278312</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E54" s="2">
+        <x:v>623558911</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:5">
+      <x:c r="A55" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C55" s="2">
+        <x:v>13301000</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E55" s="2">
+        <x:v>610257911</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:5">
+      <x:c r="A56" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C56" s="2">
+        <x:v>13582253</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E56" s="2">
+        <x:v>596675658</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:5">
+      <x:c r="A57" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C57" s="2">
+        <x:v>13301000</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E57" s="2">
+        <x:v>583374658</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:5">
+      <x:c r="A58" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C58" s="2">
+        <x:v>12301000</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E58" s="2">
+        <x:v>571073658</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:5">
+      <x:c r="A59" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C59" s="2">
+        <x:v>13143696</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E59" s="2">
+        <x:v>557929962</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:5">
+      <x:c r="A60" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C60" s="2">
+        <x:v>12797538</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E60" s="2">
+        <x:v>545132424</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:5">
+      <x:c r="A61" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C61" s="2">
+        <x:v>12797538</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E61" s="2">
+        <x:v>532334886</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:5">
+      <x:c r="A62" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C62" s="2">
+        <x:v>13143696</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E62" s="2">
+        <x:v>519191190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:5">
+      <x:c r="A63" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C63" s="2">
+        <x:v>13143696</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E63" s="2">
+        <x:v>506047494</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:5">
+      <x:c r="A64" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C64" s="2">
+        <x:v>7301000</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E64" s="2">
+        <x:v>498746494</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:5">
+      <x:c r="A65" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C65" s="2">
+        <x:v>1456600</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E65" s="2">
+        <x:v>497289894</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:5">
+      <x:c r="A66" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C66" s="2">
+        <x:v>26501700</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E66" s="2">
+        <x:v>470788194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:5">
+      <x:c r="A67" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C67" s="2">
+        <x:v>38300600</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E67" s="2">
+        <x:v>432487594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:5">
+      <x:c r="A68" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C68" s="2">
+        <x:v>30740000</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E68" s="2">
+        <x:v>401747594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:5">
+      <x:c r="A69" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D69" s="2">
+        <x:v>17334000</x:v>
+      </x:c>
+      <x:c r="E69" s="2">
+        <x:v>419081594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:5">
+      <x:c r="A70" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D70" s="2">
+        <x:v>3455000</x:v>
+      </x:c>
+      <x:c r="E70" s="2">
+        <x:v>422536594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:5">
+      <x:c r="A71" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C71" s="2">
+        <x:v>16270000</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E71" s="2">
+        <x:v>406266594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:5">
+      <x:c r="A72" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D72" s="2">
+        <x:v>636000</x:v>
+      </x:c>
+      <x:c r="E72" s="2">
+        <x:v>406902594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:5">
+      <x:c r="A73" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D73" s="2">
+        <x:v>260000</x:v>
+      </x:c>
+      <x:c r="E73" s="2">
+        <x:v>407162594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:5">
+      <x:c r="A74" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C74" s="2">
+        <x:v>12978000</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E74" s="2">
+        <x:v>394184594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:5">
+      <x:c r="A75" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C75" s="2">
+        <x:v>16270000</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E75" s="2">
+        <x:v>377914594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:5">
+      <x:c r="A76" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C76" s="2">
+        <x:v>16950000</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E76" s="2">
+        <x:v>360964594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:5">
+      <x:c r="A77" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D77" s="2">
+        <x:v>101820250</x:v>
+      </x:c>
+      <x:c r="E77" s="2">
+        <x:v>462784844</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:5">
+      <x:c r="A78" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D78" s="2">
+        <x:v>252404500</x:v>
+      </x:c>
+      <x:c r="E78" s="2">
+        <x:v>715189344</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:5">
+      <x:c r="A79" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D79" s="2">
+        <x:v>77476000</x:v>
+      </x:c>
+      <x:c r="E79" s="2">
+        <x:v>792665344</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:5">
+      <x:c r="A80" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C80" s="2">
+        <x:v>2183620</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E80" s="2">
+        <x:v>790481724</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:5">
+      <x:c r="A81" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C81" s="2">
+        <x:v>14940000</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E81" s="2">
+        <x:v>775541724</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:5">
+      <x:c r="A82" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C82" s="2">
+        <x:v>3966600</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E82" s="2">
+        <x:v>771575124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:5">
+      <x:c r="A83" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C83" s="2">
+        <x:v>14341600</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E83" s="2">
+        <x:v>757233524</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:5">
+      <x:c r="A84" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C84" s="2">
+        <x:v>4146100</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E84" s="2">
+        <x:v>753087424</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:5">
+      <x:c r="A85" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C85" s="2">
+        <x:v>66296937</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E85" s="2">
+        <x:v>686790487</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:5">
+      <x:c r="A86" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C86" s="2">
+        <x:v>19226600</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E86" s="2">
+        <x:v>667563887</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:5">
+      <x:c r="A87" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C87" s="2">
+        <x:v>57249445</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E87" s="2">
+        <x:v>610314442</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:5">
+      <x:c r="A88" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D88" s="2">
+        <x:v>636000</x:v>
+      </x:c>
+      <x:c r="E88" s="2">
+        <x:v>610950442</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:5">
+      <x:c r="A89" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C89" s="2">
+        <x:v>77772830</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E89" s="2">
+        <x:v>533177612</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:5">
+      <x:c r="A90" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C90" s="2">
+        <x:v>4256600</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E90" s="2">
+        <x:v>528921012</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:5">
+      <x:c r="A91" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C91" s="2">
+        <x:v>17139726</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E91" s="2">
+        <x:v>511781286</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:5">
+      <x:c r="A92" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D92" s="2">
+        <x:v>781000</x:v>
+      </x:c>
+      <x:c r="E92" s="2">
+        <x:v>512562286</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:5">
+      <x:c r="A93" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D93" s="2">
+        <x:v>2644000</x:v>
+      </x:c>
+      <x:c r="E93" s="2">
+        <x:v>515206286</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:5">
+      <x:c r="A94" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C94" s="2">
+        <x:v>12100</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E94" s="2">
+        <x:v>515194186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:5">
+      <x:c r="A95" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D95" s="2">
+        <x:v>2942000</x:v>
+      </x:c>
+      <x:c r="E95" s="2">
+        <x:v>518136186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:5">
+      <x:c r="A96" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D96" s="2">
+        <x:v>1143000</x:v>
+      </x:c>
+      <x:c r="E96" s="2">
+        <x:v>519279186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:5">
+      <x:c r="A97" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D97" s="2">
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="E97" s="2">
+        <x:v>519419186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:5">
+      <x:c r="A98" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D98" s="2">
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="E98" s="2">
+        <x:v>519454186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:5">
+      <x:c r="A99" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C99" s="2">
+        <x:v>28940000</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E99" s="2">
+        <x:v>490514186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:5">
+      <x:c r="A100" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C100" s="2">
+        <x:v>23470000</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E100" s="2">
+        <x:v>467044186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:5">
+      <x:c r="A101" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D101" s="2">
+        <x:v>219276800</x:v>
+      </x:c>
+      <x:c r="E101" s="2">
+        <x:v>686320986</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:5">
+      <x:c r="A102" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D102" s="2">
+        <x:v>103475300</x:v>
+      </x:c>
+      <x:c r="E102" s="2">
+        <x:v>789796286</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:5">
+      <x:c r="A103" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D103" s="2">
+        <x:v>73015850</x:v>
+      </x:c>
+      <x:c r="E103" s="2">
+        <x:v>862812136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:5">
+      <x:c r="A104" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C104" s="2">
+        <x:v>14646600</x:v>
+      </x:c>
+      <x:c r="D104" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E104" s="2">
+        <x:v>848165536</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:5">
+      <x:c r="A105" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C105" s="2">
+        <x:v>7200000</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E105" s="2">
+        <x:v>840965536</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:5">
+      <x:c r="A106" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C106" s="2">
+        <x:v>30736600</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E106" s="2">
+        <x:v>810228936</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:5">
+      <x:c r="A107" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C107" s="2">
+        <x:v>1050000</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E107" s="2">
+        <x:v>809178936</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:5">
+      <x:c r="A108" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C108" s="2">
+        <x:v>39721800</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E108" s="2">
+        <x:v>769457136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:5">
+      <x:c r="A109" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C109" s="2">
+        <x:v>2256600</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E109" s="2">
+        <x:v>767200536</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:5">
+      <x:c r="A110" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D110" s="2">
+        <x:v>15924000</x:v>
+      </x:c>
+      <x:c r="E110" s="2">
+        <x:v>783124536</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:5">
+      <x:c r="A111" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D111" s="2">
+        <x:v>588000</x:v>
+      </x:c>
+      <x:c r="E111" s="2">
+        <x:v>783712536</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:5">
+      <x:c r="A112" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D112" s="2">
+        <x:v>517000</x:v>
+      </x:c>
+      <x:c r="E112" s="2">
+        <x:v>784229536</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:5">
+      <x:c r="A113" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C113" s="2">
+        <x:v>4080600</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E113" s="2">
+        <x:v>780148936</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:5">
+      <x:c r="A114" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="C114" s="2">
+        <x:v>20006600</x:v>
+      </x:c>
+      <x:c r="D114" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E114" s="2">
+        <x:v>760142336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:5">
+      <x:c r="A115" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D115" s="2">
+        <x:v>3170000</x:v>
+      </x:c>
+      <x:c r="E115" s="2">
+        <x:v>763312336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:5">
+      <x:c r="A116" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D116" s="2">
+        <x:v>1467000</x:v>
+      </x:c>
+      <x:c r="E116" s="2">
+        <x:v>764779336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:5">
+      <x:c r="A117" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D117" s="2">
+        <x:v>2335000</x:v>
+      </x:c>
+      <x:c r="E117" s="2">
+        <x:v>767114336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:5">
+      <x:c r="A118" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C118" s="2">
+        <x:v>12851600</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E118" s="2">
+        <x:v>754262736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:5">
+      <x:c r="A119" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D119" s="2">
+        <x:v>219624000</x:v>
+      </x:c>
+      <x:c r="E119" s="2">
+        <x:v>973886736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:5">
+      <x:c r="A120" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D120" s="2">
+        <x:v>116875150</x:v>
+      </x:c>
+      <x:c r="E120" s="2">
+        <x:v>1090761886</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:5">
+      <x:c r="A121" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D121" s="2">
+        <x:v>101432400</x:v>
+      </x:c>
+      <x:c r="E121" s="2">
+        <x:v>1192194286</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:5">
+      <x:c r="A122" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C122" s="2">
+        <x:v>31900000</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E122" s="2">
+        <x:v>1160294286</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:5">
+      <x:c r="A123" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C123" s="2">
+        <x:v>10322000</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E123" s="2">
+        <x:v>1149972286</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:5">
+      <x:c r="A124" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C124" s="2">
+        <x:v>8906600</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E124" s="2">
+        <x:v>1141065686</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:5">
+      <x:c r="A125" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C125" s="2">
+        <x:v>100541587</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E125" s="2">
+        <x:v>1040524099</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:5">
+      <x:c r="A126" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C126" s="2">
+        <x:v>22730000</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E126" s="2">
+        <x:v>1017794099</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:5">
+      <x:c r="A127" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C127" s="2">
+        <x:v>31116600</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E127" s="2">
+        <x:v>986677499</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:5">
+      <x:c r="A128" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C128" s="2">
+        <x:v>34314000</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E128" s="2">
+        <x:v>952363499</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:5">
+      <x:c r="A129" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C129" s="2">
+        <x:v>29418600</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E129" s="2">
+        <x:v>922944899</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:5">
+      <x:c r="A130" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C130" s="2">
+        <x:v>31388000</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E130" s="2">
+        <x:v>891556899</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:5">
+      <x:c r="A131" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C131" s="2">
+        <x:v>19446600</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E131" s="2">
+        <x:v>872110299</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:5">
+      <x:c r="A132" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C132" s="2">
+        <x:v>34422600</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E132" s="2">
+        <x:v>837687699</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:5">
+      <x:c r="A133" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C133" s="2">
+        <x:v>4425000</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E133" s="2">
+        <x:v>833262699</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:5">
+      <x:c r="A134" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C134" s="2">
+        <x:v>22272000</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E134" s="2">
+        <x:v>810990699</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:5">
+      <x:c r="A135" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C135" s="2">
+        <x:v>2316600</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E135" s="2">
+        <x:v>808674099</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:5">
+      <x:c r="A136" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C136" s="2">
+        <x:v>2101000</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E136" s="2">
+        <x:v>806573099</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:5">
+      <x:c r="A137" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="C137" s="2">
+        <x:v>1155000</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E137" s="2">
+        <x:v>805418099</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:5">
+      <x:c r="A138" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C138" s="2">
+        <x:v>103247034</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E138" s="2">
+        <x:v>702171065</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:5">
+      <x:c r="A139" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D139" s="2">
+        <x:v>54900</x:v>
+      </x:c>
+      <x:c r="E139" s="2">
+        <x:v>702225965</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
